--- a/VerveStacks_NOR_grids_kan10/SuppXLS/Scen_TSParameters_ts_annual.xlsx
+++ b/VerveStacks_NOR_grids_kan10/SuppXLS/Scen_TSParameters_ts_annual.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NOR_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7531E255-8426-407F-81E6-4C39F0E11236}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{60BB75BF-60EB-423E-998A-33A106CF9E95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2940" yWindow="2940" windowWidth="21600" windowHeight="12682" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ev_charging_uc" sheetId="6" r:id="rId1"/>
@@ -1284,7 +1284,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0799EC7E-A5C9-4D2C-A360-7A91908570B4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED4902BF-C491-4F45-86CB-863F0618EA43}">
   <dimension ref="A9:G11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1341,7 +1341,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB11659D-B0B7-4C3D-AA64-2CF671BD0413}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89DA228C-8F4A-41B0-82CA-DE8D12A6B2D2}">
   <dimension ref="B9:O46"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2147,7 +2147,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76DB2902-0AE9-46FB-8D47-10E2C12114A4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1965D1B1-E9D5-4481-87C8-E7FD0311BFC5}">
   <dimension ref="B9:T66"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -3904,7 +3904,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2598E6A-40C3-482E-8528-349A96A94E35}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7C95608-0B04-4728-B729-2090EF3C9470}">
   <dimension ref="B9:E11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -3948,7 +3948,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AD1EE14-CEF0-4A0F-8B06-F09DA17886E6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DC6C291-AD76-4D4C-A3B8-693B6BE4E256}">
   <dimension ref="B9:D12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -3997,7 +3997,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F440C70-014E-40D7-AA4A-FC8EE58B038F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDC294DE-7F5B-4759-9BC3-7E6346A5725A}">
   <dimension ref="B9:D11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -4035,7 +4035,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6D9FB84-1B15-46A9-9543-085CDCDEB378}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{061297BF-EFB9-4AE6-9BDC-248015F64B02}">
   <dimension ref="B9:E39"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -4095,7 +4095,7 @@
         <v>37</v>
       </c>
       <c r="D13">
-        <v>0.4227999999999999</v>
+        <v>0.42280000000000001</v>
       </c>
       <c r="E13" t="s">
         <v>179</v>
@@ -4123,7 +4123,7 @@
         <v>37</v>
       </c>
       <c r="D15">
-        <v>0.43448333333333328</v>
+        <v>0.43448333333333333</v>
       </c>
       <c r="E15" t="s">
         <v>179</v>
@@ -4137,7 +4137,7 @@
         <v>37</v>
       </c>
       <c r="D16">
-        <v>0.5628833333333334</v>
+        <v>0.56288333333333329</v>
       </c>
       <c r="E16" t="s">
         <v>179</v>
@@ -4179,7 +4179,7 @@
         <v>37</v>
       </c>
       <c r="D19">
-        <v>0.52379166666666677</v>
+        <v>0.52379166666666654</v>
       </c>
       <c r="E19" t="s">
         <v>179</v>
@@ -4235,7 +4235,7 @@
         <v>37</v>
       </c>
       <c r="D23">
-        <v>0.51214166666666661</v>
+        <v>0.51214166666666672</v>
       </c>
       <c r="E23" t="s">
         <v>179</v>
@@ -4263,7 +4263,7 @@
         <v>37</v>
       </c>
       <c r="D25">
-        <v>0.49735000000000001</v>
+        <v>0.49734999999999996</v>
       </c>
       <c r="E25" t="s">
         <v>179</v>
@@ -4291,7 +4291,7 @@
         <v>37</v>
       </c>
       <c r="D27">
-        <v>0.4890416666666666</v>
+        <v>0.48904166666666676</v>
       </c>
       <c r="E27" t="s">
         <v>179</v>
@@ -4333,7 +4333,7 @@
         <v>37</v>
       </c>
       <c r="D30">
-        <v>0.44539166666666663</v>
+        <v>0.44539166666666669</v>
       </c>
       <c r="E30" t="s">
         <v>179</v>
@@ -4347,7 +4347,7 @@
         <v>37</v>
       </c>
       <c r="D31">
-        <v>0.41229999999999994</v>
+        <v>0.41230000000000006</v>
       </c>
       <c r="E31" t="s">
         <v>179</v>
@@ -4375,7 +4375,7 @@
         <v>37</v>
       </c>
       <c r="D33">
-        <v>0.47183333333333338</v>
+        <v>0.47183333333333333</v>
       </c>
       <c r="E33" t="s">
         <v>179</v>
@@ -4389,7 +4389,7 @@
         <v>37</v>
       </c>
       <c r="D34">
-        <v>0.45400000000000001</v>
+        <v>0.45399999999999996</v>
       </c>
       <c r="E34" t="s">
         <v>179</v>
